--- a/data/trans_bre/P2A_lim_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P2A_lim_R-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 2,36</t>
+          <t>-4,88; 2,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 10,56</t>
+          <t>-2,05; 11,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 9,67</t>
+          <t>-0,64; 10,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 7,89</t>
+          <t>-2,39; 7,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-73,2; 99,36</t>
+          <t>-73,75; 93,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-14,56; 103,0</t>
+          <t>-14,97; 114,27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-11,89; 167,44</t>
+          <t>-11,33; 174,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-17,12; 89,35</t>
+          <t>-17,37; 85,46</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 4,79</t>
+          <t>-3,29; 4,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 4,33</t>
+          <t>-3,41; 4,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 4,08</t>
+          <t>-1,28; 3,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 4,42</t>
+          <t>-5,7; 4,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-26,14; 58,91</t>
+          <t>-26,09; 62,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-29,29; 53,44</t>
+          <t>-29,68; 54,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-27,56; 144,07</t>
+          <t>-25,46; 133,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-27,1; 26,44</t>
+          <t>-25,08; 25,48</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 3,13</t>
+          <t>-2,29; 2,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 4,54</t>
+          <t>-5,05; 4,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 5,38</t>
+          <t>-0,02; 5,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,24; 1,59</t>
+          <t>-8,29; 1,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-58,36; 192,67</t>
+          <t>-59,05; 175,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-39,99; 67,06</t>
+          <t>-41,91; 65,85</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-14,27; 550,85</t>
+          <t>-17,5; 469,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-41,81; 12,52</t>
+          <t>-41,49; 12,4</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 3,54</t>
+          <t>-3,39; 3,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,38; 10,4</t>
+          <t>1,22; 10,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 7,57</t>
+          <t>-2,55; 7,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,72; 1,48</t>
+          <t>-7,21; 1,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-47,0; 85,09</t>
+          <t>-45,39; 94,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,98; 193,91</t>
+          <t>7,76; 192,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-18,57; 90,93</t>
+          <t>-19,71; 85,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-63,74; 24,2</t>
+          <t>-61,96; 27,48</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 8,91</t>
+          <t>-3,01; 9,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 10,25</t>
+          <t>-6,59; 10,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 5,1</t>
+          <t>-5,0; 5,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 5,05</t>
+          <t>-5,83; 4,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-32,71; 119,65</t>
+          <t>-27,09; 129,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-23,57; 63,02</t>
+          <t>-26,84; 68,32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-47,06; 94,22</t>
+          <t>-48,37; 94,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-46,65; 77,02</t>
+          <t>-49,09; 75,71</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 4,27</t>
+          <t>-0,82; 4,36</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 10,1</t>
+          <t>0,16; 10,92</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 7,36</t>
+          <t>-3,79; 7,26</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-6,46; 6,05</t>
+          <t>-6,69; 5,39</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-44,84; 871,59</t>
+          <t>-48,34; 708,47</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 182,22</t>
+          <t>-4,14; 185,81</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-32,78; 95,38</t>
+          <t>-30,26; 94,25</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-23,39; 29,16</t>
+          <t>-23,81; 25,42</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 4,01</t>
+          <t>-2,3; 3,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 4,29</t>
+          <t>-2,31; 4,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 4,73</t>
+          <t>-0,92; 4,79</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,44; 56,42</t>
+          <t>1,36; 54,5</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-23,99; 69,91</t>
+          <t>-26,35; 64,11</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-20,06; 69,02</t>
+          <t>-22,76; 69,49</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-16,82; 108,55</t>
+          <t>-15,49; 120,11</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,92; 499,89</t>
+          <t>8,07; 400,54</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,47; 6,58</t>
+          <t>0,46; 6,28</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 3,9</t>
+          <t>-2,04; 3,71</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 3,26</t>
+          <t>-2,63; 3,63</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,9; 8,58</t>
+          <t>0,91; 8,2</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,61; 97,72</t>
+          <t>4,3; 92,72</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-23,97; 59,63</t>
+          <t>-21,61; 60,63</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-26,74; 45,76</t>
+          <t>-25,39; 51,35</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>10,46; 266,61</t>
+          <t>12,12; 268,18</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,07; 2,69</t>
+          <t>0,0; 2,65</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,45; 3,55</t>
+          <t>0,59; 3,53</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,92</t>
+          <t>0,35; 3,02</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,38; 20,58</t>
+          <t>0,26; 21,7</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,46; 44,83</t>
+          <t>-0,0; 44,34</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,5; 41,62</t>
+          <t>5,91; 40,93</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,3; 46,53</t>
+          <t>4,5; 47,37</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,86; 191,86</t>
+          <t>1,94; 181,22</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_lim_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P2A_lim_R-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,9</t>
+          <t>2,48</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>23,13%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 2,02</t>
+          <t>-4,36; 2,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 11,19</t>
+          <t>-1,57; 10,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 10,01</t>
+          <t>-1,09; 9,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 7,73</t>
+          <t>-2,38; 6,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-73,75; 93,68</t>
+          <t>-73,29; 102,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-14,97; 114,27</t>
+          <t>-10,28; 109,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-11,33; 174,15</t>
+          <t>-12,28; 160,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-17,37; 85,46</t>
+          <t>-17,09; 80,95</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,53</t>
+          <t>-0,46</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-2,76%</t>
+          <t>-2,43%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 4,9</t>
+          <t>-3,74; 4,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 4,3</t>
+          <t>-3,52; 4,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 3,94</t>
+          <t>-1,43; 4,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 4,05</t>
+          <t>-5,49; 4,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-26,09; 62,83</t>
+          <t>-30,15; 58,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-29,68; 54,12</t>
+          <t>-29,39; 50,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-25,46; 133,67</t>
+          <t>-25,41; 164,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-25,08; 25,48</t>
+          <t>-24,25; 27,76</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-3,17</t>
+          <t>-3,12</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-19,48%</t>
+          <t>-19,36%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 2,84</t>
+          <t>-2,39; 2,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,05; 4,68</t>
+          <t>-5,14; 4,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 5,16</t>
+          <t>0,08; 5,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,29; 1,64</t>
+          <t>-7,64; 1,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-59,05; 175,62</t>
+          <t>-61,98; 188,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-41,91; 65,85</t>
+          <t>-41,17; 64,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-17,5; 469,97</t>
+          <t>-10,99; 545,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-41,49; 12,4</t>
+          <t>-40,62; 13,86</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-2,45</t>
+          <t>-1,35</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-30,19%</t>
+          <t>-16,32%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 3,69</t>
+          <t>-3,14; 3,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,22; 10,38</t>
+          <t>1,61; 10,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 7,62</t>
+          <t>-1,89; 7,88</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,21; 1,52</t>
+          <t>-6,21; 2,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-45,39; 94,6</t>
+          <t>-44,74; 99,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,76; 192,81</t>
+          <t>16,59; 205,61</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-19,71; 85,45</t>
+          <t>-14,44; 94,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-61,96; 27,48</t>
+          <t>-51,98; 52,41</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,54</t>
+          <t>3,02</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>38,42%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 9,44</t>
+          <t>-3,09; 9,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 10,09</t>
+          <t>-6,25; 10,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 5,51</t>
+          <t>-4,99; 5,85</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 4,83</t>
+          <t>-0,84; 6,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-27,09; 129,72</t>
+          <t>-25,67; 128,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-26,84; 68,32</t>
+          <t>-24,67; 62,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-48,37; 94,79</t>
+          <t>-46,62; 114,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-49,09; 75,71</t>
+          <t>-10,51; 120,26</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-0,6</t>
+          <t>-0,87</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-2,45%</t>
+          <t>-3,54%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 4,36</t>
+          <t>-0,85; 4,35</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,16; 10,92</t>
+          <t>0,06; 10,78</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 7,26</t>
+          <t>-3,93; 7,36</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 5,39</t>
+          <t>-6,86; 5,28</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-48,34; 708,47</t>
+          <t>-53,04; 790,71</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 185,81</t>
+          <t>-3,02; 176,16</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-30,26; 94,25</t>
+          <t>-31,36; 94,82</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-23,81; 25,42</t>
+          <t>-25,01; 24,67</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22,44</t>
+          <t>3,55</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>142,24%</t>
+          <t>22,06%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 3,5</t>
+          <t>-2,01; 3,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 4,54</t>
+          <t>-2,22; 4,16</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 4,79</t>
+          <t>-0,69; 5,19</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,36; 54,5</t>
+          <t>-0,39; 8,04</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-26,35; 64,11</t>
+          <t>-23,89; 69,44</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-22,76; 69,49</t>
+          <t>-23,77; 63,94</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-15,49; 120,11</t>
+          <t>-12,14; 125,9</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,07; 400,54</t>
+          <t>-2,23; 58,24</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3,93</t>
+          <t>2,2</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>28,19%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,46; 6,28</t>
+          <t>0,69; 6,55</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 3,71</t>
+          <t>-2,04; 3,59</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 3,63</t>
+          <t>-2,54; 3,51</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,91; 8,2</t>
+          <t>-0,65; 4,69</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,3; 92,72</t>
+          <t>6,77; 95,96</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-21,61; 60,63</t>
+          <t>-22,4; 55,6</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-25,39; 51,35</t>
+          <t>-23,73; 48,01</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>12,12; 268,18</t>
+          <t>-7,7; 70,22</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5,71</t>
+          <t>0,96</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>7,09%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,65</t>
+          <t>0,15; 2,71</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,53</t>
+          <t>0,43; 3,62</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,02</t>
+          <t>0,46; 3,04</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,26; 21,7</t>
+          <t>-0,6; 2,4</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 44,34</t>
+          <t>1,9; 45,75</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,91; 40,93</t>
+          <t>4,09; 41,78</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,5; 47,37</t>
+          <t>6,53; 48,15</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,94; 181,22</t>
+          <t>-4,1; 18,98</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_lim_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P2A_lim_R-Provincia-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con alguna limitación</t>
+          <t>Población que convive con personas con alguna limitación (física, sensorial o psíquica)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
